--- a/output/satyam_full.xlsx
+++ b/output/satyam_full.xlsx
@@ -1049,7 +1049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA71"/>
+  <dimension ref="A1:AB71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1079,6 +1079,7 @@
     <col width="34" customWidth="1" min="25" max="25"/>
     <col width="19" customWidth="1" min="26" max="26"/>
     <col width="29" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1217,6 +1218,11 @@
           <t>Results (initial) indicator</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>source_file_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -1311,6 +1317,9 @@
       <c r="AA2" t="n">
         <v/>
       </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -1405,6 +1414,9 @@
       <c r="AA3" t="n">
         <v/>
       </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1499,6 +1511,9 @@
       <c r="AA4" t="n">
         <v/>
       </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -1593,6 +1608,9 @@
       <c r="AA5" t="n">
         <v/>
       </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1687,6 +1705,9 @@
       <c r="AA6" t="n">
         <v/>
       </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -1781,6 +1802,9 @@
       <c r="AA7" t="n">
         <v/>
       </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1875,6 +1899,9 @@
       <c r="AA8" t="n">
         <v/>
       </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1969,6 +1996,9 @@
       <c r="AA9" t="n">
         <v/>
       </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -2063,6 +2093,9 @@
       <c r="AA10" t="n">
         <v/>
       </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -2157,6 +2190,9 @@
       <c r="AA11" t="n">
         <v/>
       </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -2251,6 +2287,9 @@
       <c r="AA12" t="n">
         <v/>
       </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -2345,6 +2384,9 @@
       <c r="AA13" t="n">
         <v/>
       </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -2439,6 +2481,9 @@
       <c r="AA14" t="n">
         <v/>
       </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -2533,6 +2578,9 @@
       <c r="AA15" t="n">
         <v/>
       </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -2627,6 +2675,9 @@
       <c r="AA16" t="n">
         <v/>
       </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -2721,6 +2772,9 @@
       <c r="AA17" t="n">
         <v/>
       </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -2815,6 +2869,9 @@
       <c r="AA18" t="n">
         <v/>
       </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -2909,6 +2966,9 @@
       <c r="AA19" t="n">
         <v/>
       </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -3003,6 +3063,9 @@
       <c r="AA20" t="n">
         <v/>
       </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -3097,6 +3160,9 @@
       <c r="AA21" t="n">
         <v/>
       </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -3191,6 +3257,9 @@
       <c r="AA22" t="n">
         <v/>
       </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -3290,6 +3359,9 @@
       <c r="AA23" t="n">
         <v/>
       </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -3384,6 +3456,9 @@
       <c r="AA24" t="n">
         <v/>
       </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -3478,6 +3553,9 @@
       <c r="AA25" t="n">
         <v/>
       </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -3577,6 +3655,9 @@
       <c r="AA26" t="n">
         <v/>
       </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -3671,6 +3752,9 @@
       <c r="AA27" t="n">
         <v/>
       </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -3765,6 +3849,9 @@
       <c r="AA28" t="n">
         <v/>
       </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -3859,6 +3946,9 @@
       <c r="AA29" t="n">
         <v/>
       </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -3953,6 +4043,9 @@
       <c r="AA30" t="n">
         <v/>
       </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -4047,6 +4140,9 @@
       <c r="AA31" t="n">
         <v/>
       </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -4141,6 +4237,9 @@
       <c r="AA32" t="n">
         <v/>
       </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -4235,6 +4334,9 @@
       <c r="AA33" t="n">
         <v/>
       </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -4329,6 +4431,9 @@
       <c r="AA34" t="n">
         <v/>
       </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -4423,6 +4528,9 @@
       <c r="AA35" t="n">
         <v/>
       </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -4517,6 +4625,9 @@
       <c r="AA36" t="n">
         <v/>
       </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
@@ -4611,6 +4722,9 @@
       <c r="AA37" t="n">
         <v/>
       </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -4705,6 +4819,9 @@
       <c r="AA38" t="n">
         <v/>
       </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -4799,6 +4916,9 @@
       <c r="AA39" t="n">
         <v/>
       </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -4893,6 +5013,9 @@
       <c r="AA40" t="n">
         <v/>
       </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -4987,6 +5110,9 @@
       <c r="AA41" t="n">
         <v/>
       </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -5081,6 +5207,9 @@
       <c r="AA42" t="n">
         <v/>
       </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -5175,6 +5304,9 @@
       <c r="AA43" t="n">
         <v/>
       </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -5269,6 +5401,9 @@
       <c r="AA44" t="n">
         <v/>
       </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -5363,6 +5498,9 @@
       <c r="AA45" t="n">
         <v/>
       </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -5457,6 +5595,9 @@
       <c r="AA46" t="n">
         <v/>
       </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -5551,6 +5692,9 @@
       <c r="AA47" t="n">
         <v/>
       </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -5645,6 +5789,9 @@
       <c r="AA48" t="n">
         <v/>
       </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -5739,6 +5886,9 @@
       <c r="AA49" t="n">
         <v/>
       </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -5833,6 +5983,9 @@
       <c r="AA50" t="n">
         <v/>
       </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -5927,6 +6080,9 @@
       <c r="AA51" t="n">
         <v/>
       </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -6021,6 +6177,9 @@
       <c r="AA52" t="n">
         <v/>
       </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -6115,6 +6274,9 @@
       <c r="AA53" t="n">
         <v/>
       </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -6209,6 +6371,9 @@
       <c r="AA54" t="n">
         <v/>
       </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -6303,6 +6468,9 @@
       <c r="AA55" t="n">
         <v/>
       </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -6397,6 +6565,9 @@
       <c r="AA56" t="n">
         <v/>
       </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -6491,6 +6662,9 @@
       <c r="AA57" t="n">
         <v/>
       </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -6585,6 +6759,9 @@
       <c r="AA58" t="n">
         <v/>
       </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -6679,6 +6856,9 @@
       <c r="AA59" t="n">
         <v/>
       </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -6773,6 +6953,9 @@
       <c r="AA60" t="n">
         <v/>
       </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -6867,6 +7050,9 @@
       <c r="AA61" t="n">
         <v/>
       </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -6961,6 +7147,9 @@
       <c r="AA62" t="n">
         <v/>
       </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -7055,6 +7244,9 @@
       <c r="AA63" t="n">
         <v/>
       </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
@@ -7149,6 +7341,9 @@
       <c r="AA64" t="n">
         <v/>
       </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
@@ -7243,6 +7438,9 @@
       <c r="AA65" t="n">
         <v/>
       </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
@@ -7337,6 +7535,9 @@
       <c r="AA66" t="n">
         <v/>
       </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
@@ -7431,6 +7632,9 @@
       <c r="AA67" t="n">
         <v/>
       </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
@@ -7525,6 +7729,9 @@
       <c r="AA68" t="n">
         <v/>
       </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -7619,6 +7826,9 @@
       <c r="AA69" t="n">
         <v/>
       </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
@@ -7713,6 +7923,9 @@
       <c r="AA70" t="n">
         <v/>
       </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
@@ -7806,6 +8019,9 @@
       </c>
       <c r="AA71" t="n">
         <v/>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -18268,12 +18484,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
@@ -18413,7 +18629,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml - p1 - travel interest &gt; </t>
+          <t>fml-p1-002 &gt; coding languages – copy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -18470,7 +18686,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml p1 engaged shoppers + travel adventure [01-12-25] &gt; </t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -18479,7 +18695,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>118171.8760061444</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -18490,7 +18706,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -18498,36 +18714,30 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>116987</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>9404.320714285714</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>1.08741482157467</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>8.741482157467049</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml- am2 &gt; </t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -18536,7 +18746,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>22068.2419047619</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -18547,7 +18757,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -18555,36 +18765,30 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>3617.046428571426</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1.08741482157467</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>8.741482157467043</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml- cbo- s &gt; </t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -18593,7 +18797,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>56950.30168970814</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -18604,7 +18808,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -18612,36 +18816,30 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>71992</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>5787.274285714288</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>1.087414821574671</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>8.741482157467054</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-5a-3c-002 &gt; </t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -18650,7 +18848,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>34526.12039938556</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -18661,7 +18859,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -18669,36 +18867,30 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>17998</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>1446.818571428572</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1.087414821574671</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>8.741482157467054</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-abo-c1 &gt; </t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -18707,7 +18899,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>851.4197635135137</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -18755,7 +18947,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-abo-c2 &gt; </t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -18764,7 +18956,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>49552.63023648649</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -18775,7 +18967,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -18783,25 +18975,19 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>-5409.050000000003</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0.8926862027952118</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>-10.73137972047882</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>10080.81</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -18812,7 +18998,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-am-abo-campaign &gt; </t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -18832,7 +19018,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -18840,10 +19026,10 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>26997</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>26997</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -18862,14 +19048,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-am1-abo &gt; </t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -18889,7 +19075,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -18897,10 +19083,10 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>62993</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>62993</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -18919,14 +19105,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-bdc-acc-test &gt; </t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -18946,7 +19132,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -18954,10 +19140,10 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -18976,14 +19162,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-c1-002 &gt; </t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -19003,7 +19189,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -19011,10 +19197,10 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -19033,14 +19219,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-c1-broad - corporates &gt; </t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -19060,7 +19246,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -19068,10 +19254,10 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>35996</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>35996</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -19090,3796 +19276,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c1-broad - engaged shoppers &gt; </t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c1-broad - job &amp; career &gt; </t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c1-broad - job interests &gt; </t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c1-broad - travel interests &gt; </t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c1-broad - travel interests – copy &gt; </t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c1-wn &gt; </t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c1-wn [03-01-26] &gt; </t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c2-002 [08-12-25] &gt; </t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c2-broad - travel &gt; </t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c2-cbo-002 &gt; </t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c2-wn &gt; </t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c3-002 &gt; </t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c3-abo-002 [09-12-25] &gt; </t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c3-wn [09-02-26 ] &gt; </t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c3-wn- cbo [05-01-26] &gt; </t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo 1 &gt; </t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo 2 &gt; </t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo-3 &gt; </t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo-4 &gt; </t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo-5 &gt; </t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo-c1 [03-11-25] &gt; </t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo-p2 &gt; </t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo-test &gt; </t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo-test – copy &gt; </t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cprg-cbo-p1 [12-12-25] cprg &gt; </t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-p1-002 &gt; </t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-p1-002 – copy _ cprg &gt; </t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-p1-broad - job &amp; career &gt; </t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-p2-002 &gt; </t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-p2-002 – copy &gt; </t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-retargeting - showup &gt; </t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-target test &gt; </t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-test campaign &gt; </t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-test-002 &gt; </t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-test-1nov &gt; </t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-test-campaign &gt; </t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-test-campaign-all &gt; </t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-test-instant-form &gt; </t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; </t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>231716.54</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>13</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>116987</v>
-      </c>
-      <c r="I54" s="4" t="n">
-        <v>9404.320714285714</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>1.08741482157467</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>8.741482157467049</v>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>8275.590714285714</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
           <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>5</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I55" s="4" t="n">
-        <v>3617.046428571426</v>
-      </c>
-      <c r="J55" s="5" t="n">
-        <v>1.08741482157467</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>8.741482157467043</v>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>8275.590714285714</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>8</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>71992</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>5787.274285714288</v>
-      </c>
-      <c r="J56" s="5" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>8275.590714285714</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>2</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I57" s="4" t="n">
-        <v>1446.818571428572</v>
-      </c>
-      <c r="J57" s="5" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K57" s="6" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>8275.590714285714</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 2103 &gt; </t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 2103 cbo [22-4-26] &gt; </t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 2103 cbo lla &lt;&gt; s2 &gt; </t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 2103 cbo lla &lt;&gt; s3 &gt; </t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 2103 cbo s2 &gt; </t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; cbo &lt;&gt; cc297623 | images &gt; </t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; </t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>50404.05</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>5</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I65" s="7" t="n">
-        <v>-5409.050000000003</v>
-      </c>
-      <c r="J65" s="5" t="n">
-        <v>0.8926862027952118</v>
-      </c>
-      <c r="K65" s="6" t="n">
-        <v>-10.73137972047882</v>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>10080.81</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>3</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I66" s="4" t="n">
-        <v>26997</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>7</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>62993</v>
-      </c>
-      <c r="I67" s="4" t="n">
-        <v>62993</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; ry &lt;&gt; 11/06 &lt;&gt; abo &gt; </t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I69" s="4" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I70" s="4" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremostleads + rky+ 09/04 &gt; </t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremostleads + rky+ 19/04 &gt; </t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremostleads + rky+ 22/04 &gt; </t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremostleads-gs-13-09 &gt; </t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>4</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>35996</v>
-      </c>
-      <c r="I75" s="4" t="n">
-        <v>35996</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremostleads-gs-13-09 7 video ads &gt; </t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremostleads-gs-13-09- simple image ads &gt; </t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremostleads-gs-13-09-10-video ads &gt; </t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">formost leads &lt;&gt; video &lt;&gt; talking head &lt;&gt; cbo | 74852 &gt; </t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">new leads campaign &gt; </t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">retargeting-campaign [22-12-25] &gt; </t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
@@ -22894,12 +19291,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
@@ -23039,7 +19436,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml - p1 - travel interest &gt;  &gt; </t>
+          <t>fml-p1-002 &gt; coding languages – copy &gt; abhishekpal-ad 2 hook 6-1;1 ratio-311025-006</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -23096,7 +19493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml p1 engaged shoppers + travel adventure [01-12-25] &gt;  &gt; </t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience &gt; split screen &lt;&gt; germany is actively hiring international talent right now &gt;</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -23105,7 +19502,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>118171.8760061444</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -23116,7 +19513,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -23124,36 +19521,30 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>116987</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>9404.320714285714</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>1.08741482157467</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>8.741482157467049</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml- am2 &gt;  &gt; </t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy &gt; image ad &lt;&gt; sticky note &lt;&gt; join this masterclass, dubai's tech sector is growing fast and sponsoring visas now</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -23162,7 +19553,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>22068.2419047619</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -23173,7 +19564,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -23181,36 +19572,30 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>3617.046428571426</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1.08741482157467</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>8.741482157467043</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml- cbo- s &gt;  &gt; </t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -23219,7 +19604,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>28593.79730670763</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -23230,7 +19615,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -23238,36 +19623,30 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>3617.046428571426</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>1.08741482157467</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>8.741482157467043</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-5a-3c-002 &gt;  &gt; </t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; if you want a it job abroad in 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -23276,7 +19655,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>949.1716948284691</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -23324,7 +19703,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-abo-c1 &gt;  &gt; </t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; what if i get rejected my english not that good &lt;&gt; navy blue blazer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -23333,7 +19712,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>27407.33268817205</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -23344,7 +19723,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -23352,36 +19731,30 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>26997</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>2170.227857142858</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1.087414821574671</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>8.741482157467054</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-abo-c2 &gt;  &gt; </t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; laptop screen | if you're an it professional in india &amp; looking to get</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -23390,7 +19763,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>118.6464618535586</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -23438,7 +19811,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-am-abo-campaign &gt;  &gt; </t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -23447,7 +19820,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0</v>
+        <v>34407.47393753201</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -23458,7 +19831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -23466,36 +19839,30 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>17998</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>1446.818571428572</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1.087414821574671</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>8.741482157467054</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-am1-abo &gt;  &gt; </t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -23504,7 +19871,7 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>851.4197635135137</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -23552,7 +19919,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-bdc-acc-test &gt;  &gt; </t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -23561,7 +19928,7 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>49552.63023648649</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -23572,7 +19939,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -23580,25 +19947,19 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>-5409.050000000003</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0.8926862027952118</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>-10.73137972047882</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>10080.81</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -23609,7 +19970,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-c1-002 &gt;  &gt; </t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -23629,7 +19990,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -23637,10 +19998,10 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>26997</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>26997</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -23659,14 +20020,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-c1-broad - corporates &gt;  &gt; </t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -23686,7 +20047,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -23694,10 +20055,10 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>62993</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>62993</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -23716,14 +20077,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-c1-broad - engaged shoppers &gt;  &gt; </t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -23743,7 +20104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -23751,10 +20112,10 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -23773,14 +20134,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-c1-broad - job &amp; career &gt;  &gt; </t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -23800,7 +20161,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -23808,10 +20169,10 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -23830,14 +20191,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-c1-broad - job interests &gt;  &gt; </t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -23857,7 +20218,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -23865,10 +20226,10 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>26997</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>26997</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -23887,14 +20248,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">fml-c1-broad - travel interests &gt;  &gt; </t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -23914,7 +20275,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -23922,10 +20283,10 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -23944,3676 +20305,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c1-broad - travel interests – copy &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c1-wn &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c1-wn [03-01-26] &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c2-002 [08-12-25] &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c2-broad - travel &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c2-cbo-002 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c2-wn &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c3-002 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c3-abo-002 [09-12-25] &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c3-wn [09-02-26 ] &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-c3-wn- cbo [05-01-26] &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo 1 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo 2 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo-3 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo-4 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo-5 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo-c1 [03-11-25] &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo-p2 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo-test &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cbo-test – copy &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-cprg-cbo-p1 [12-12-25] cprg &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-p1-002 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-p1-002 – copy _ cprg &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-p1-broad - job &amp; career &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-p2-002 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-p2-002 – copy &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-retargeting - showup &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-target test &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-test campaign &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-test-002 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-test-1nov &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-test-campaign &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-test-campaign-all &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fml-test-instant-form &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>231716.54</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience &gt; split screen &lt;&gt; germany is actively hiring international talent right now &gt;</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>13</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>116987</v>
-      </c>
-      <c r="I54" s="4" t="n">
-        <v>9404.320714285714</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>1.08741482157467</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>8.741482157467049</v>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>8275.590714285714</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
           <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy &gt; image ad &lt;&gt; sticky note &lt;&gt; join this masterclass, dubai's tech sector is growing fast and sponsoring visas now</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>5</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I55" s="4" t="n">
-        <v>3617.046428571426</v>
-      </c>
-      <c r="J55" s="5" t="n">
-        <v>1.08741482157467</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>8.741482157467043</v>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>8275.590714285714</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>5</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>3617.046428571426</v>
-      </c>
-      <c r="J56" s="5" t="n">
-        <v>1.08741482157467</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>8.741482157467043</v>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>8275.590714285714</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; what if i get rejected my english not that good &lt;&gt; navy blue blazer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>3</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I57" s="4" t="n">
-        <v>2170.227857142858</v>
-      </c>
-      <c r="J57" s="5" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K57" s="6" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>8275.590714285714</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I58" s="4" t="n">
-        <v>1446.818571428572</v>
-      </c>
-      <c r="J58" s="5" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>8275.590714285714</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 2103 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 2103 cbo [22-4-26] &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 2103 cbo lla &lt;&gt; s2 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 2103 cbo lla &lt;&gt; s3 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 2103 cbo s2 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; cbo &lt;&gt; cc297623 | images &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>50404.05</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>5</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I66" s="7" t="n">
-        <v>-5409.050000000003</v>
-      </c>
-      <c r="J66" s="5" t="n">
-        <v>0.8926862027952118</v>
-      </c>
-      <c r="K66" s="6" t="n">
-        <v>-10.73137972047882</v>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>10080.81</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>3</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I67" s="4" t="n">
-        <v>26997</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>7</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>62993</v>
-      </c>
-      <c r="I68" s="4" t="n">
-        <v>62993</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; ry &lt;&gt; 11/06 &lt;&gt; abo &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I70" s="4" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I71" s="4" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremostleads + rky+ 09/04 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremostleads + rky+ 19/04 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremostleads + rky+ 22/04 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremostleads-gs-13-09 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I76" s="4" t="n">
-        <v>26997</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I77" s="4" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremostleads-gs-13-09 7 video ads &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremostleads-gs-13-09- simple image ads &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">foremostleads-gs-13-09-10-video ads &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">formost leads &lt;&gt; video &lt;&gt; talking head &lt;&gt; cbo | 74852 &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">new leads campaign &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">retargeting-campaign [22-12-25] &gt;  &gt; </t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>

--- a/output/satyam_full.xlsx
+++ b/output/satyam_full.xlsx
@@ -8035,7 +8035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -8120,11 +8120,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C:52.0, AS:52.0, AD:52.0</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
+          <t>C:49.0, AS:49.0, AD:49.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8140,7 +8142,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -8148,11 +8150,13 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C:467948.0, AS:467948.0, AD:467948.0</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
+          <t>C:440951.0, AS:440951.0, AD:440951.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -8425,6 +8429,422 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>Count of sales that still lack a valid sale date</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>G. Total Sales</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>52</v>
+      </c>
+      <c r="D15" t="n">
+        <v>52</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Total Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>G. Attributed Sales</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>49</v>
+      </c>
+      <c r="D16" t="n">
+        <v>49</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Attributed Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>G. Unattributed Sales</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Unattributed Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>G. Total Revenue</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>467948</v>
+      </c>
+      <c r="D18" t="n">
+        <v>467948</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>G. Attributed Revenue</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>440951</v>
+      </c>
+      <c r="D19" t="n">
+        <v>440951</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Attributed Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>G. Unattributed Revenue</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>26997</v>
+      </c>
+      <c r="D20" t="n">
+        <v>26997</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Unattributed Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>G. Raw Meta Spend</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>456047.55</v>
+      </c>
+      <c r="D21" t="n">
+        <v>282120.59</v>
+      </c>
+      <c r="E21" t="n">
+        <v>173926.96</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Raw Meta Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>G. Attributed Spend</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>282120.59</v>
+      </c>
+      <c r="D22" t="n">
+        <v>282120.59</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Attributed Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>G. Unallocated Spend</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>173926.96</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>173926.96</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Unallocated Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>G. Profit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>158830.41</v>
+      </c>
+      <c r="D24" t="n">
+        <v>158830.41</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>G. ROAS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Golden Report verification for ROAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>G. ROI %</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Golden Report verification for ROI %</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>G. CAC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5757.56</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5757.56</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Golden Report verification for CAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>INV. Revenue Formula</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Attributed + Unattributed = Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>INV. Spend Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Attributed + Unallocated = Raw Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>INV. Profit Formula</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Attributed Revenue - Attributed Spend = Profit</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -14545,7 +14965,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>foremost leads | cbo | 14th august</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Primary</t>
@@ -14563,7 +14987,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -14571,10 +14995,10 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -14600,7 +15024,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august</t>
+          <t>foremost leads | cbo | 11th august 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -14657,7 +15081,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026</t>
+          <t>fml-test-instant-form</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -14677,7 +15101,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -14685,10 +15109,10 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -14707,14 +15131,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fml-p2-002 – copy</t>
+          <t>fml-test-campaign-all</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -14771,7 +15195,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fml-retargeting - showup</t>
+          <t>fml-test-campaign</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -14828,7 +15252,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fml-p2-002</t>
+          <t>fml-test-1nov</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -14885,7 +15309,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fml-target test</t>
+          <t>fml - p1 - travel interest</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -14942,7 +15366,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fml-test campaign</t>
+          <t>foremost leads &lt;&gt; 2103</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -14999,7 +15423,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103</t>
+          <t>fml-test campaign</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -15056,7 +15480,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fml-test-1nov</t>
+          <t>fml-target test</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -15113,7 +15537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fml-p1-broad - job &amp; career</t>
+          <t>fml-retargeting - showup</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -15170,7 +15594,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fml-p1-002 – copy _ cprg</t>
+          <t>fml-p2-002 – copy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -15227,7 +15651,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fml-test-campaign</t>
+          <t>fml-p2-002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -15284,7 +15708,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fml-test-campaign-all</t>
+          <t>fml-p1-broad - job &amp; career</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -15341,7 +15765,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fml-test-instant-form</t>
+          <t>fml-p1-002 – copy _ cprg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -15626,7 +16050,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fml-cprg-cbo-p1 [12-12-25] cprg</t>
+          <t>fml p1 engaged shoppers + travel adventure [01-12-25]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -16367,7 +16791,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fml-cbo-test – copy</t>
+          <t>fml-cprg-cbo-p1 [12-12-25] cprg</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16424,7 +16848,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>fml - p1 - travel interest</t>
+          <t>fml-cbo-test – copy</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -16481,7 +16905,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>fml-cbo-test</t>
+          <t>fml-bdc-acc-test</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -16880,7 +17304,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>fml-bdc-acc-test</t>
+          <t>fml-am1-abo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -16937,7 +17361,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>fml-am1-abo</t>
+          <t>fml-c1-wn</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -17336,7 +17760,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>fml p1 engaged shoppers + travel adventure [01-12-25]</t>
+          <t>fml-c1-broad - travel interests – copy</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -17393,7 +17817,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fml-c1-broad - travel interests – copy</t>
+          <t>fml-c1-wn [03-01-26]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -17450,7 +17874,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>fml-c1-wn</t>
+          <t>fml-cbo-test</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -17507,7 +17931,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>fml-c1-wn [03-01-26]</t>
+          <t>fml-cbo 1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -17564,7 +17988,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>fml-cbo 1</t>
+          <t>fml-cbo-p2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -17621,7 +18045,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>fml-cbo-p2</t>
+          <t>fml-cbo-c1 [03-11-25]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -17678,7 +18102,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>fml-cbo-c1 [03-11-25]</t>
+          <t>fml-cbo-5</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -17735,7 +18159,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fml-cbo-5</t>
+          <t>fml-cbo-4</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -17792,7 +18216,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fml-cbo-4</t>
+          <t>fml-cbo-3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -17849,7 +18273,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>fml-cbo-3</t>
+          <t>fml-cbo 2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -17906,7 +18330,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>fml-cbo 2</t>
+          <t>fml-c3-wn- cbo [05-01-26]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -17963,7 +18387,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>fml-c3-wn- cbo [05-01-26]</t>
+          <t>fml-c2-002 [08-12-25]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -18020,7 +18444,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>fml-c2-002 [08-12-25]</t>
+          <t>fml-c3-wn [09-02-26 ]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -18077,7 +18501,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>fml-c3-wn [09-02-26 ]</t>
+          <t>fml-c3-abo-002 [09-12-25]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -18134,7 +18558,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>fml-c3-abo-002 [09-12-25]</t>
+          <t>fml-c3-002</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -18191,7 +18615,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>fml-c3-002</t>
+          <t>fml-c2-wn</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -18248,7 +18672,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>fml-c2-wn</t>
+          <t>fml-c2-cbo-002</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -18305,7 +18729,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>fml-c2-cbo-002</t>
+          <t>fml-c2-broad - travel</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -18362,7 +18786,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>fml-c2-broad - travel</t>
+          <t>retargeting-campaign [22-12-25]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -18411,63 +18835,6 @@
         </is>
       </c>
       <c r="M73" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>retargeting-campaign [22-12-25]</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -18484,7 +18851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -18572,7 +18939,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &gt; </t>
+          <t>fml-p1-002 &gt; coding languages – copy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -18592,7 +18959,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -18600,10 +18967,10 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>26997</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -18622,14 +18989,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fml-p1-002 &gt; coding languages – copy</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -18638,7 +19005,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>118171.8760061444</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -18649,7 +19016,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -18657,36 +19024,30 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>116987</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>9404.320714285714</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>1.08741482157467</v>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>8.741482157467049</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -18695,7 +19056,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>118171.8760061444</v>
+        <v>22068.2419047619</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -18706,7 +19067,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -18714,16 +19075,16 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>116987</v>
+        <v>44995</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>9404.320714285714</v>
+        <v>3617.046428571426</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>1.08741482157467</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>8.741482157467049</v>
+        <v>8.741482157467043</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>8275.590714285714</v>
@@ -18737,7 +19098,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -18746,7 +19107,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>22068.2419047619</v>
+        <v>56950.30168970814</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -18757,7 +19118,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -18765,16 +19126,16 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>44995</v>
+        <v>71992</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3617.046428571426</v>
+        <v>5787.274285714288</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1.08741482157467</v>
+        <v>1.087414821574671</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>8.741482157467043</v>
+        <v>8.741482157467054</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>8275.590714285714</v>
@@ -18788,7 +19149,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -18797,7 +19158,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>56950.30168970814</v>
+        <v>34526.12039938556</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -18808,7 +19169,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -18816,10 +19177,10 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>71992</v>
+        <v>17998</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5787.274285714288</v>
+        <v>1446.818571428572</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>1.087414821574671</v>
@@ -18839,7 +19200,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -18848,7 +19209,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>34526.12039938556</v>
+        <v>851.4197635135137</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -18859,7 +19220,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -18867,30 +19228,36 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>1446.818571428572</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -18899,7 +19266,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>851.4197635135137</v>
+        <v>49552.63023648649</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -18910,7 +19277,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -18918,25 +19285,19 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>-5409.050000000003</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.8926862027952118</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>-10.73137972047882</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>10080.81</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -18947,7 +19308,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -18956,7 +19317,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>49552.63023648649</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -18967,7 +19328,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -18975,30 +19336,36 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>-5409.050000000003</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>0.8926862027952118</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>-10.73137972047882</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>10080.81</v>
+        <v>26997</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>26997</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -19018,7 +19385,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -19026,10 +19393,10 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>26997</v>
+        <v>62993</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>26997</v>
+        <v>62993</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -19055,7 +19422,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -19075,7 +19442,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -19083,10 +19450,10 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>62993</v>
+        <v>8999</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>62993</v>
+        <v>8999</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -19112,7 +19479,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55</t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -19169,7 +19536,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -19189,7 +19556,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -19197,10 +19564,10 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>8999</v>
+        <v>35996</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>8999</v>
+        <v>35996</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -19218,63 +19585,6 @@
         </is>
       </c>
       <c r="M13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>35996</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>35996</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -19291,7 +19601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -19379,7 +19689,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &gt;  &gt; </t>
+          <t>fml-p1-002 &gt; coding languages – copy &gt; abhishekpal-ad 2 hook 6-1;1 ratio-311025-006</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -19399,7 +19709,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -19407,10 +19717,10 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>26997</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -19429,14 +19739,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fml-p1-002 &gt; coding languages – copy &gt; abhishekpal-ad 2 hook 6-1;1 ratio-311025-006</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience &gt; split screen &lt;&gt; germany is actively hiring international talent right now &gt;</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19445,7 +19755,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>118171.8760061444</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -19456,7 +19766,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -19464,36 +19774,30 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>116987</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>9404.320714285714</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>1.08741482157467</v>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>8.741482157467049</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience &gt; split screen &lt;&gt; germany is actively hiring international talent right now &gt;</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy &gt; image ad &lt;&gt; sticky note &lt;&gt; join this masterclass, dubai's tech sector is growing fast and sponsoring visas now</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -19502,7 +19806,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>118171.8760061444</v>
+        <v>22068.2419047619</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -19513,7 +19817,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -19521,16 +19825,16 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>116987</v>
+        <v>44995</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>9404.320714285714</v>
+        <v>3617.046428571426</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>1.08741482157467</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>8.741482157467049</v>
+        <v>8.741482157467043</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>8275.590714285714</v>
@@ -19544,7 +19848,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy &gt; image ad &lt;&gt; sticky note &lt;&gt; join this masterclass, dubai's tech sector is growing fast and sponsoring visas now</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -19553,7 +19857,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>22068.2419047619</v>
+        <v>28593.79730670763</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -19595,7 +19899,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; if you want a it job abroad in 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -19604,7 +19908,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>28593.79730670763</v>
+        <v>949.1716948284691</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -19615,7 +19919,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -19623,30 +19927,36 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>3617.046428571426</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>1.08741482157467</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>8.741482157467043</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; if you want a it job abroad in 2026</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; what if i get rejected my english not that good &lt;&gt; navy blue blazer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -19655,7 +19965,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>949.1716948284691</v>
+        <v>27407.33268817205</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -19666,7 +19976,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -19674,36 +19984,30 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>26997</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>2170.227857142858</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1.087414821574671</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>8.741482157467054</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; what if i get rejected my english not that good &lt;&gt; navy blue blazer</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; laptop screen | if you're an it professional in india &amp; looking to get</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -19712,7 +20016,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>27407.33268817205</v>
+        <v>118.6464618535586</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -19723,7 +20027,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -19731,30 +20035,36 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>2170.227857142858</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; laptop screen | if you're an it professional in india &amp; looking to get</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -19763,7 +20073,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>118.6464618535586</v>
+        <v>34407.47393753201</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -19774,7 +20084,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -19782,36 +20092,30 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>17998</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>1446.818571428572</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>1.087414821574671</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>8.741482157467054</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -19820,7 +20124,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>34407.47393753201</v>
+        <v>851.4197635135137</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -19831,7 +20135,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -19839,30 +20143,36 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>1446.818571428572</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -19871,7 +20181,7 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>851.4197635135137</v>
+        <v>49552.63023648649</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -19882,7 +20192,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -19890,25 +20200,19 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>-5409.050000000003</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0.8926862027952118</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>-10.73137972047882</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>10080.81</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -19919,7 +20223,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -19928,7 +20232,7 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>49552.63023648649</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -19939,7 +20243,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -19947,30 +20251,36 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>-5409.050000000003</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>0.8926862027952118</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>-10.73137972047882</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>10080.81</v>
+        <v>26997</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>26997</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -19990,7 +20300,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -19998,10 +20308,10 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>26997</v>
+        <v>62993</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>26997</v>
+        <v>62993</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -20027,7 +20337,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -20047,7 +20357,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -20055,10 +20365,10 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>62993</v>
+        <v>8999</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>62993</v>
+        <v>8999</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -20084,7 +20394,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -20141,7 +20451,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -20161,7 +20471,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -20169,10 +20479,10 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>8999</v>
+        <v>26997</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>8999</v>
+        <v>26997</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -20198,7 +20508,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -20218,7 +20528,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -20226,10 +20536,10 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -20247,63 +20557,6 @@
         </is>
       </c>
       <c r="M17" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -20320,14 +20573,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Raw Meta Spend</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>282120.59</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Attributed Spend</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>282120.59</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Unallocated Spend</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20340,14 +20633,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Funnel Stage</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total Leads</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Paid Leads</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Unpaid Leads</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/satyam_full.xlsx
+++ b/output/satyam_full.xlsx
@@ -83,9 +83,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>97.8129117259552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.187088274044796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1584,7 +1584,7 @@
   <dimension ref="A1:AB71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -1757,8 +1757,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>46242</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1825,7 +1827,7 @@
       <c r="S2" t="n">
         <v/>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="T2" s="6" t="n">
         <v/>
       </c>
       <c r="U2" t="n">
@@ -1854,8 +1856,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46242</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1922,7 +1926,7 @@
       <c r="S3" t="n">
         <v/>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="T3" s="6" t="n">
         <v/>
       </c>
       <c r="U3" t="n">
@@ -1951,8 +1955,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>46242</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2019,7 +2025,7 @@
       <c r="S4" t="n">
         <v/>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="T4" s="6" t="n">
         <v/>
       </c>
       <c r="U4" t="n">
@@ -2048,8 +2054,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>46242</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2116,7 +2124,7 @@
       <c r="S5" t="n">
         <v/>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="T5" s="6" t="n">
         <v/>
       </c>
       <c r="U5" t="n">
@@ -2145,8 +2153,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46242</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2213,7 +2223,7 @@
       <c r="S6" t="n">
         <v/>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="T6" s="6" t="n">
         <v/>
       </c>
       <c r="U6" t="n">
@@ -2242,8 +2252,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>46242</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2310,7 +2322,7 @@
       <c r="S7" t="n">
         <v/>
       </c>
-      <c r="T7" s="4" t="n">
+      <c r="T7" s="6" t="n">
         <v/>
       </c>
       <c r="U7" t="n">
@@ -2339,8 +2351,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>46242</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2407,7 +2421,7 @@
       <c r="S8" t="n">
         <v/>
       </c>
-      <c r="T8" s="4" t="n">
+      <c r="T8" s="6" t="n">
         <v/>
       </c>
       <c r="U8" t="n">
@@ -2436,8 +2450,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46242</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2504,7 +2520,7 @@
       <c r="S9" t="n">
         <v/>
       </c>
-      <c r="T9" s="4" t="n">
+      <c r="T9" s="6" t="n">
         <v/>
       </c>
       <c r="U9" t="n">
@@ -2533,8 +2549,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46242</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2601,7 +2619,7 @@
       <c r="S10" t="n">
         <v/>
       </c>
-      <c r="T10" s="4" t="n">
+      <c r="T10" s="6" t="n">
         <v/>
       </c>
       <c r="U10" t="n">
@@ -2630,8 +2648,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>46242</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2698,7 +2718,7 @@
       <c r="S11" t="n">
         <v/>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="T11" s="6" t="n">
         <v/>
       </c>
       <c r="U11" t="n">
@@ -2727,8 +2747,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>46242</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2795,7 +2817,7 @@
       <c r="S12" t="n">
         <v/>
       </c>
-      <c r="T12" s="4" t="n">
+      <c r="T12" s="6" t="n">
         <v/>
       </c>
       <c r="U12" t="n">
@@ -2824,8 +2846,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>46242</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2892,7 +2916,7 @@
       <c r="S13" t="n">
         <v/>
       </c>
-      <c r="T13" s="4" t="n">
+      <c r="T13" s="6" t="n">
         <v/>
       </c>
       <c r="U13" t="n">
@@ -2921,8 +2945,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>46242</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2989,7 +3015,7 @@
       <c r="S14" t="n">
         <v/>
       </c>
-      <c r="T14" s="4" t="n">
+      <c r="T14" s="6" t="n">
         <v/>
       </c>
       <c r="U14" t="n">
@@ -3018,8 +3044,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>46242</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3086,7 +3114,7 @@
       <c r="S15" t="n">
         <v/>
       </c>
-      <c r="T15" s="4" t="n">
+      <c r="T15" s="6" t="n">
         <v/>
       </c>
       <c r="U15" t="n">
@@ -3115,8 +3143,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>46242</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3183,7 +3213,7 @@
       <c r="S16" t="n">
         <v/>
       </c>
-      <c r="T16" s="4" t="n">
+      <c r="T16" s="6" t="n">
         <v/>
       </c>
       <c r="U16" t="n">
@@ -3212,8 +3242,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46242</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3280,7 +3312,7 @@
       <c r="S17" t="n">
         <v/>
       </c>
-      <c r="T17" s="4" t="n">
+      <c r="T17" s="6" t="n">
         <v/>
       </c>
       <c r="U17" t="n">
@@ -3309,8 +3341,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>46242</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3377,7 +3411,7 @@
       <c r="S18" t="n">
         <v/>
       </c>
-      <c r="T18" s="4" t="n">
+      <c r="T18" s="6" t="n">
         <v/>
       </c>
       <c r="U18" t="n">
@@ -3406,8 +3440,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>46242</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3474,7 +3510,7 @@
       <c r="S19" t="n">
         <v/>
       </c>
-      <c r="T19" s="4" t="n">
+      <c r="T19" s="6" t="n">
         <v/>
       </c>
       <c r="U19" t="n">
@@ -3503,8 +3539,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>46242</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3571,7 +3609,7 @@
       <c r="S20" t="n">
         <v/>
       </c>
-      <c r="T20" s="4" t="n">
+      <c r="T20" s="6" t="n">
         <v/>
       </c>
       <c r="U20" t="n">
@@ -3600,8 +3638,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>46242</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3668,7 +3708,7 @@
       <c r="S21" t="n">
         <v/>
       </c>
-      <c r="T21" s="4" t="n">
+      <c r="T21" s="6" t="n">
         <v/>
       </c>
       <c r="U21" t="n">
@@ -3697,8 +3737,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46242</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3765,7 +3807,7 @@
       <c r="S22" t="n">
         <v/>
       </c>
-      <c r="T22" s="4" t="n">
+      <c r="T22" s="6" t="n">
         <v/>
       </c>
       <c r="U22" t="n">
@@ -3794,8 +3836,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>46242</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3867,7 +3911,7 @@
       <c r="S23" t="n">
         <v>14.684191</v>
       </c>
-      <c r="T23" s="4" t="n">
+      <c r="T23" s="6" t="n">
         <v>0.731637</v>
       </c>
       <c r="U23" t="n">
@@ -3896,8 +3940,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>46242</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3964,7 +4010,7 @@
       <c r="S24" t="n">
         <v/>
       </c>
-      <c r="T24" s="4" t="n">
+      <c r="T24" s="6" t="n">
         <v/>
       </c>
       <c r="U24" t="n">
@@ -3993,8 +4039,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>46242</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -4061,7 +4109,7 @@
       <c r="S25" t="n">
         <v/>
       </c>
-      <c r="T25" s="4" t="n">
+      <c r="T25" s="6" t="n">
         <v/>
       </c>
       <c r="U25" t="n">
@@ -4090,8 +4138,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>46242</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -4163,7 +4213,7 @@
       <c r="S26" t="n">
         <v>15.736513</v>
       </c>
-      <c r="T26" s="4" t="n">
+      <c r="T26" s="6" t="n">
         <v>0.517593</v>
       </c>
       <c r="U26" t="n">
@@ -4192,8 +4242,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46242</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -4260,7 +4312,7 @@
       <c r="S27" t="n">
         <v/>
       </c>
-      <c r="T27" s="4" t="n">
+      <c r="T27" s="6" t="n">
         <v/>
       </c>
       <c r="U27" t="n">
@@ -4289,8 +4341,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>46242</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -4357,7 +4411,7 @@
       <c r="S28" t="n">
         <v/>
       </c>
-      <c r="T28" s="4" t="n">
+      <c r="T28" s="6" t="n">
         <v/>
       </c>
       <c r="U28" t="n">
@@ -4386,8 +4440,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>46242</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -4454,7 +4510,7 @@
       <c r="S29" t="n">
         <v/>
       </c>
-      <c r="T29" s="4" t="n">
+      <c r="T29" s="6" t="n">
         <v/>
       </c>
       <c r="U29" t="n">
@@ -4483,8 +4539,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>46242</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -4551,7 +4609,7 @@
       <c r="S30" t="n">
         <v/>
       </c>
-      <c r="T30" s="4" t="n">
+      <c r="T30" s="6" t="n">
         <v/>
       </c>
       <c r="U30" t="n">
@@ -4580,8 +4638,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>46242</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4648,7 +4708,7 @@
       <c r="S31" t="n">
         <v/>
       </c>
-      <c r="T31" s="4" t="n">
+      <c r="T31" s="6" t="n">
         <v/>
       </c>
       <c r="U31" t="n">
@@ -4677,8 +4737,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>46242</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4745,7 +4807,7 @@
       <c r="S32" t="n">
         <v/>
       </c>
-      <c r="T32" s="4" t="n">
+      <c r="T32" s="6" t="n">
         <v/>
       </c>
       <c r="U32" t="n">
@@ -4774,8 +4836,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>46242</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4842,7 +4906,7 @@
       <c r="S33" t="n">
         <v/>
       </c>
-      <c r="T33" s="4" t="n">
+      <c r="T33" s="6" t="n">
         <v/>
       </c>
       <c r="U33" t="n">
@@ -4871,8 +4935,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>46242</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4939,7 +5005,7 @@
       <c r="S34" t="n">
         <v/>
       </c>
-      <c r="T34" s="4" t="n">
+      <c r="T34" s="6" t="n">
         <v/>
       </c>
       <c r="U34" t="n">
@@ -4968,8 +5034,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>46242</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -5036,7 +5104,7 @@
       <c r="S35" t="n">
         <v/>
       </c>
-      <c r="T35" s="4" t="n">
+      <c r="T35" s="6" t="n">
         <v/>
       </c>
       <c r="U35" t="n">
@@ -5065,8 +5133,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>46242</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -5133,7 +5203,7 @@
       <c r="S36" t="n">
         <v/>
       </c>
-      <c r="T36" s="4" t="n">
+      <c r="T36" s="6" t="n">
         <v/>
       </c>
       <c r="U36" t="n">
@@ -5162,8 +5232,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>46242</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -5230,7 +5302,7 @@
       <c r="S37" t="n">
         <v/>
       </c>
-      <c r="T37" s="4" t="n">
+      <c r="T37" s="6" t="n">
         <v/>
       </c>
       <c r="U37" t="n">
@@ -5259,8 +5331,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>46242</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -5327,7 +5401,7 @@
       <c r="S38" t="n">
         <v/>
       </c>
-      <c r="T38" s="4" t="n">
+      <c r="T38" s="6" t="n">
         <v/>
       </c>
       <c r="U38" t="n">
@@ -5356,8 +5430,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>46242</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5424,7 +5500,7 @@
       <c r="S39" t="n">
         <v/>
       </c>
-      <c r="T39" s="4" t="n">
+      <c r="T39" s="6" t="n">
         <v/>
       </c>
       <c r="U39" t="n">
@@ -5453,8 +5529,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>46242</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5521,7 +5599,7 @@
       <c r="S40" t="n">
         <v/>
       </c>
-      <c r="T40" s="4" t="n">
+      <c r="T40" s="6" t="n">
         <v/>
       </c>
       <c r="U40" t="n">
@@ -5550,8 +5628,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>46242</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5618,7 +5698,7 @@
       <c r="S41" t="n">
         <v/>
       </c>
-      <c r="T41" s="4" t="n">
+      <c r="T41" s="6" t="n">
         <v/>
       </c>
       <c r="U41" t="n">
@@ -5647,8 +5727,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>46242</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5715,7 +5797,7 @@
       <c r="S42" t="n">
         <v/>
       </c>
-      <c r="T42" s="4" t="n">
+      <c r="T42" s="6" t="n">
         <v/>
       </c>
       <c r="U42" t="n">
@@ -5744,8 +5826,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>46242</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5812,7 +5896,7 @@
       <c r="S43" t="n">
         <v/>
       </c>
-      <c r="T43" s="4" t="n">
+      <c r="T43" s="6" t="n">
         <v/>
       </c>
       <c r="U43" t="n">
@@ -5841,8 +5925,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>46242</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5909,7 +5995,7 @@
       <c r="S44" t="n">
         <v/>
       </c>
-      <c r="T44" s="4" t="n">
+      <c r="T44" s="6" t="n">
         <v/>
       </c>
       <c r="U44" t="n">
@@ -5938,8 +6024,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>46242</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -6006,7 +6094,7 @@
       <c r="S45" t="n">
         <v/>
       </c>
-      <c r="T45" s="4" t="n">
+      <c r="T45" s="6" t="n">
         <v/>
       </c>
       <c r="U45" t="n">
@@ -6035,8 +6123,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
-        <v>46242</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -6103,7 +6193,7 @@
       <c r="S46" t="n">
         <v/>
       </c>
-      <c r="T46" s="4" t="n">
+      <c r="T46" s="6" t="n">
         <v/>
       </c>
       <c r="U46" t="n">
@@ -6132,8 +6222,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>46242</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -6200,7 +6292,7 @@
       <c r="S47" t="n">
         <v/>
       </c>
-      <c r="T47" s="4" t="n">
+      <c r="T47" s="6" t="n">
         <v/>
       </c>
       <c r="U47" t="n">
@@ -6229,8 +6321,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
-        <v>46242</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -6297,7 +6391,7 @@
       <c r="S48" t="n">
         <v/>
       </c>
-      <c r="T48" s="4" t="n">
+      <c r="T48" s="6" t="n">
         <v/>
       </c>
       <c r="U48" t="n">
@@ -6326,8 +6420,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
-        <v>46242</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6394,7 +6490,7 @@
       <c r="S49" t="n">
         <v/>
       </c>
-      <c r="T49" s="4" t="n">
+      <c r="T49" s="6" t="n">
         <v/>
       </c>
       <c r="U49" t="n">
@@ -6423,8 +6519,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
-        <v>46242</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6491,7 +6589,7 @@
       <c r="S50" t="n">
         <v/>
       </c>
-      <c r="T50" s="4" t="n">
+      <c r="T50" s="6" t="n">
         <v/>
       </c>
       <c r="U50" t="n">
@@ -6520,8 +6618,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>46242</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6588,7 +6688,7 @@
       <c r="S51" t="n">
         <v/>
       </c>
-      <c r="T51" s="4" t="n">
+      <c r="T51" s="6" t="n">
         <v/>
       </c>
       <c r="U51" t="n">
@@ -6617,8 +6717,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
-        <v>46242</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6685,7 +6787,7 @@
       <c r="S52" t="n">
         <v/>
       </c>
-      <c r="T52" s="4" t="n">
+      <c r="T52" s="6" t="n">
         <v/>
       </c>
       <c r="U52" t="n">
@@ -6714,8 +6816,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>46242</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6782,7 +6886,7 @@
       <c r="S53" t="n">
         <v/>
       </c>
-      <c r="T53" s="4" t="n">
+      <c r="T53" s="6" t="n">
         <v/>
       </c>
       <c r="U53" t="n">
@@ -6811,8 +6915,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>46242</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6879,7 +6985,7 @@
       <c r="S54" t="n">
         <v/>
       </c>
-      <c r="T54" s="4" t="n">
+      <c r="T54" s="6" t="n">
         <v/>
       </c>
       <c r="U54" t="n">
@@ -6908,8 +7014,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
-        <v>46242</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6976,7 +7084,7 @@
       <c r="S55" t="n">
         <v/>
       </c>
-      <c r="T55" s="4" t="n">
+      <c r="T55" s="6" t="n">
         <v/>
       </c>
       <c r="U55" t="n">
@@ -7005,8 +7113,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
-        <v>46242</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -7073,7 +7183,7 @@
       <c r="S56" t="n">
         <v/>
       </c>
-      <c r="T56" s="4" t="n">
+      <c r="T56" s="6" t="n">
         <v/>
       </c>
       <c r="U56" t="n">
@@ -7102,8 +7212,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>46242</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -7170,7 +7282,7 @@
       <c r="S57" t="n">
         <v/>
       </c>
-      <c r="T57" s="4" t="n">
+      <c r="T57" s="6" t="n">
         <v/>
       </c>
       <c r="U57" t="n">
@@ -7199,8 +7311,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>46242</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -7267,7 +7381,7 @@
       <c r="S58" t="n">
         <v/>
       </c>
-      <c r="T58" s="4" t="n">
+      <c r="T58" s="6" t="n">
         <v/>
       </c>
       <c r="U58" t="n">
@@ -7296,8 +7410,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>46242</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -7364,7 +7480,7 @@
       <c r="S59" t="n">
         <v/>
       </c>
-      <c r="T59" s="4" t="n">
+      <c r="T59" s="6" t="n">
         <v/>
       </c>
       <c r="U59" t="n">
@@ -7393,8 +7509,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>46242</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -7461,7 +7579,7 @@
       <c r="S60" t="n">
         <v/>
       </c>
-      <c r="T60" s="4" t="n">
+      <c r="T60" s="6" t="n">
         <v/>
       </c>
       <c r="U60" t="n">
@@ -7490,8 +7608,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
-        <v>46242</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -7558,7 +7678,7 @@
       <c r="S61" t="n">
         <v/>
       </c>
-      <c r="T61" s="4" t="n">
+      <c r="T61" s="6" t="n">
         <v/>
       </c>
       <c r="U61" t="n">
@@ -7587,8 +7707,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>46242</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -7655,7 +7777,7 @@
       <c r="S62" t="n">
         <v/>
       </c>
-      <c r="T62" s="4" t="n">
+      <c r="T62" s="6" t="n">
         <v/>
       </c>
       <c r="U62" t="n">
@@ -7684,8 +7806,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
-        <v>46242</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -7752,7 +7876,7 @@
       <c r="S63" t="n">
         <v/>
       </c>
-      <c r="T63" s="4" t="n">
+      <c r="T63" s="6" t="n">
         <v/>
       </c>
       <c r="U63" t="n">
@@ -7781,8 +7905,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>46242</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -7849,7 +7975,7 @@
       <c r="S64" t="n">
         <v/>
       </c>
-      <c r="T64" s="4" t="n">
+      <c r="T64" s="6" t="n">
         <v/>
       </c>
       <c r="U64" t="n">
@@ -7878,8 +8004,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
-        <v>46242</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -7946,7 +8074,7 @@
       <c r="S65" t="n">
         <v/>
       </c>
-      <c r="T65" s="4" t="n">
+      <c r="T65" s="6" t="n">
         <v/>
       </c>
       <c r="U65" t="n">
@@ -7975,8 +8103,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
-        <v>46242</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -8043,7 +8173,7 @@
       <c r="S66" t="n">
         <v/>
       </c>
-      <c r="T66" s="4" t="n">
+      <c r="T66" s="6" t="n">
         <v/>
       </c>
       <c r="U66" t="n">
@@ -8072,8 +8202,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
-        <v>46242</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -8140,7 +8272,7 @@
       <c r="S67" t="n">
         <v/>
       </c>
-      <c r="T67" s="4" t="n">
+      <c r="T67" s="6" t="n">
         <v/>
       </c>
       <c r="U67" t="n">
@@ -8169,8 +8301,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
-        <v>46242</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -8237,7 +8371,7 @@
       <c r="S68" t="n">
         <v/>
       </c>
-      <c r="T68" s="4" t="n">
+      <c r="T68" s="6" t="n">
         <v/>
       </c>
       <c r="U68" t="n">
@@ -8266,8 +8400,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
-        <v>46242</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -8334,7 +8470,7 @@
       <c r="S69" t="n">
         <v/>
       </c>
-      <c r="T69" s="4" t="n">
+      <c r="T69" s="6" t="n">
         <v/>
       </c>
       <c r="U69" t="n">
@@ -8363,8 +8499,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
-        <v>46242</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -8431,7 +8569,7 @@
       <c r="S70" t="n">
         <v/>
       </c>
-      <c r="T70" s="4" t="n">
+      <c r="T70" s="6" t="n">
         <v/>
       </c>
       <c r="U70" t="n">
@@ -8460,8 +8598,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
-        <v>46242</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -8528,7 +8668,7 @@
       <c r="S71" t="n">
         <v/>
       </c>
-      <c r="T71" s="4" t="n">
+      <c r="T71" s="6" t="n">
         <v/>
       </c>
       <c r="U71" t="n">
@@ -8810,10 +8950,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3795</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>3795</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15298,16 +15438,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -15398,27 +15538,31 @@
         <v>231716.54</v>
       </c>
       <c r="D2" t="n">
-        <v>1992</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>28</v>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>1.405622489959839</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H2" s="2" t="n">
         <v>251972</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="4" t="n">
         <v>20255.45999999999</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="J2" s="5" t="n">
         <v>1.08741482157467</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="K2" s="6" t="n">
         <v>8.741482157467047</v>
       </c>
       <c r="L2" s="2" t="n">
@@ -15445,21 +15589,25 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>732</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>9</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>1.229508196721312</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H3" s="2" t="n">
         <v>80991</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="4" t="n">
         <v>80991</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -15498,16 +15646,20 @@
         <v>50404.05</v>
       </c>
       <c r="D4" t="n">
-        <v>598</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="4" t="n">
-        <v>0.8361204013377926</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H4" s="2" t="n">
         <v>44995</v>
@@ -15515,10 +15667,10 @@
       <c r="I4" s="7" t="n">
         <v>-5409.050000000003</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="5" t="n">
         <v>0.8926862027952118</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K4" s="6" t="n">
         <v>-10.73137972047882</v>
       </c>
       <c r="L4" s="2" t="n">
@@ -15545,21 +15697,25 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>243</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>1.646090534979424</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H5" s="2" t="n">
         <v>35996</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="4" t="n">
         <v>35996</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -15586,7 +15742,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>foremost leads | cbo | 11th august 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -15598,21 +15754,25 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>3.448275862068965</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H6" s="2" t="n">
         <v>8999</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="4" t="n">
         <v>8999</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -15639,7 +15799,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026</t>
+          <t>foremost leads | cbo | 14th august</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -15651,21 +15811,25 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>1.666666666666667</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H7" s="2" t="n">
         <v>8999</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="4" t="n">
         <v>8999</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -15692,7 +15856,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august</t>
+          <t>--</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -15704,21 +15868,25 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>5.555555555555555</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H8" s="2" t="n">
         <v>8999</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I8" s="4" t="n">
         <v>8999</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -15745,7 +15913,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fml-test-campaign</t>
+          <t>fml-retargeting - showup</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -15802,7 +15970,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost</t>
+          <t>fml-target test</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -15814,16 +15982,20 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="4" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H10" s="2" t="n">
         <v>0</v>
@@ -15855,7 +16027,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fml-test-instant-form</t>
+          <t>fml-test campaign</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -15912,7 +16084,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fml-test-campaign-all</t>
+          <t>foremost leads &lt;&gt; 2103</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -15969,7 +16141,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fml-test-1nov</t>
+          <t>fml-p2-002 – copy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -16026,7 +16198,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103 cbo [22-4-26]</t>
+          <t>fml-p2-002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -16083,7 +16255,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fml-test-002</t>
+          <t>fml-test-1nov</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -16140,7 +16312,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fml-test campaign</t>
+          <t>fml-p1-broad - job &amp; career</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -16197,7 +16369,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fml-target test</t>
+          <t>fml-p1-002 – copy _ cprg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -16254,7 +16426,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fml-retargeting - showup</t>
+          <t>fml-test-campaign</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -16311,7 +16483,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fml-p2-002 – copy</t>
+          <t>fml-test-campaign-all</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -16368,7 +16540,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fml-p2-002</t>
+          <t>fml-test-instant-form</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -16425,7 +16597,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fml-p1-broad - job &amp; career</t>
+          <t>fml-test-002</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -16482,7 +16654,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103</t>
+          <t>foremost leads &lt;&gt; 2103 cbo lla &lt;&gt; s3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -16539,7 +16711,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103 cbo s2</t>
+          <t>foremost leads &lt;&gt; 2103 cbo [22-4-26]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -16653,7 +16825,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103 cbo lla &lt;&gt; s3</t>
+          <t>fml-cprg-cbo-p1 [12-12-25] cprg</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -16710,7 +16882,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fml-p1-002</t>
+          <t>foremost leads &lt;&gt; 2103 cbo s2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -16722,16 +16894,20 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H26" s="2" t="n">
         <v>0</v>
@@ -16877,7 +17053,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026</t>
+          <t>foremostleads + rky+ 09/04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -16889,16 +17065,20 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>69</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H29" s="2" t="n">
         <v>0</v>
@@ -16930,7 +17110,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>foremostleads + rky+ 09/04</t>
+          <t>foremostleads + rky+ 19/04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -16987,7 +17167,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>foremostleads + rky+ 19/04</t>
+          <t>foremostleads + rky+ 22/04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -17044,7 +17224,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>foremostleads + rky+ 22/04</t>
+          <t>foremostleads-gs-13-09 7 video ads</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -17101,7 +17281,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 7 video ads</t>
+          <t>foremostleads-gs-13-09- simple image ads</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -17158,7 +17338,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09- simple image ads</t>
+          <t>foremostleads-gs-13-09-10-video ads</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -17215,7 +17395,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09-10-video ads</t>
+          <t>formost leads &lt;&gt; video &lt;&gt; talking head &lt;&gt; cbo | 74852</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -17272,7 +17452,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>formost leads &lt;&gt; video &lt;&gt; talking head &lt;&gt; cbo | 74852</t>
+          <t>new leads campaign</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -17329,7 +17509,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>new leads campaign</t>
+          <t>fml-p1-002</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -17386,7 +17566,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>retargeting-campaign [22-12-25]</t>
+          <t>fml-cbo-test – copy</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -17443,7 +17623,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>fml-p1-002 – copy _ cprg</t>
+          <t>fml - p1 - travel interest</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17500,7 +17680,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>fml-cprg-cbo-p1 [12-12-25] cprg</t>
+          <t>fml-cbo-test</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17557,7 +17737,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>chatgpt.com</t>
+          <t>fml-c1-broad - travel interests</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -17569,16 +17749,20 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="4" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H41" s="2" t="n">
         <v>0</v>
@@ -17610,7 +17794,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fml-am1-abo</t>
+          <t>fml-c1-broad - job interests</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -17667,7 +17851,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>fml-c1-broad - travel interests</t>
+          <t>fml-c1-broad - job &amp; career</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -17724,7 +17908,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>fml-c1-broad - job interests</t>
+          <t>fml-c1-broad - engaged shoppers</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -17781,7 +17965,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>fml-c1-broad - job &amp; career</t>
+          <t>fml-c1-broad - corporates</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -17838,7 +18022,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>fml-c1-broad - engaged shoppers</t>
+          <t>fml-c1-002</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -17895,7 +18079,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>fml-c1-broad - corporates</t>
+          <t>fml-bdc-acc-test</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -17952,7 +18136,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>fml-c1-002</t>
+          <t>fml-am1-abo</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -18009,7 +18193,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>fml-bdc-acc-test</t>
+          <t>fml-am-abo-campaign</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -18066,7 +18250,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fml-am-abo-campaign</t>
+          <t>fml-abo-c2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -18123,7 +18307,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fml-cbo-test – copy</t>
+          <t>fml-abo-c1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -18180,7 +18364,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>fml-abo-c2</t>
+          <t>fml-5a-3c-002</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -18237,7 +18421,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>fml-abo-c1</t>
+          <t>fml- cbo- s</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -18294,7 +18478,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>fml-5a-3c-002</t>
+          <t>fml- am2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -18351,7 +18535,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>fml- cbo- s</t>
+          <t>fml p1 engaged shoppers + travel adventure [01-12-25]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -18408,7 +18592,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fml- am2</t>
+          <t>fml-c1-broad - travel interests – copy</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -18465,7 +18649,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>fml p1 engaged shoppers + travel adventure [01-12-25]</t>
+          <t>fml-c1-wn</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -18522,7 +18706,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>fml - p1 - travel interest</t>
+          <t>fml-c1-wn [03-01-26]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -18579,7 +18763,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>fml-c1-broad - travel interests – copy</t>
+          <t>fml-cbo 1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -18636,7 +18820,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>fml-c1-wn</t>
+          <t>fml-cbo-p2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -18693,7 +18877,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>fml-c1-wn [03-01-26]</t>
+          <t>fml-cbo-c1 [03-11-25]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -18750,7 +18934,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fml-c2-002 [08-12-25]</t>
+          <t>fml-cbo-5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -18807,7 +18991,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fml-cbo-test</t>
+          <t>fml-cbo-4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -18864,7 +19048,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>fml-cbo-p2</t>
+          <t>fml-cbo-3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -18921,7 +19105,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>fml-cbo-c1 [03-11-25]</t>
+          <t>fml-cbo 2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -18978,7 +19162,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>fml-cbo-5</t>
+          <t>fml-c3-wn- cbo [05-01-26]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -19035,7 +19219,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>fml-cbo-4</t>
+          <t>fml-c2-002 [08-12-25]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -19092,7 +19276,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>fml-cbo-3</t>
+          <t>fml-c3-wn [09-02-26 ]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -19149,7 +19333,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>fml-cbo 2</t>
+          <t>fml-c3-abo-002 [09-12-25]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -19206,7 +19390,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>fml-cbo 1</t>
+          <t>fml-c3-002</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -19263,7 +19447,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>fml-c3-wn- cbo [05-01-26]</t>
+          <t>fml-c2-wn</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -19320,7 +19504,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>fml-c3-wn [09-02-26 ]</t>
+          <t>fml-c2-cbo-002</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -19377,7 +19561,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>fml-c3-abo-002 [09-12-25]</t>
+          <t>fml-c2-broad - travel</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -19434,7 +19618,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>fml-c3-002</t>
+          <t>retargeting-campaign [22-12-25]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -19483,230 +19667,6 @@
         </is>
       </c>
       <c r="M74" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>fml-c2-wn</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>fml-c2-cbo-002</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>fml-c2-broad - travel</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>{{campaign.name}}</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" t="n">
-        <v>51</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -19723,16 +19683,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -19823,21 +19783,25 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>3.448275862068965</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H2" s="2" t="n">
         <v>8999</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="4" t="n">
         <v>8999</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -19864,7 +19828,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>chatgpt.com &gt; --</t>
+          <t>fml-p1-002 &gt; coding languages – copy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19876,16 +19840,20 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H3" s="2" t="n">
         <v>0</v>
@@ -19917,7 +19885,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fml-p1-002 &gt; coding languages – copy</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -19926,40 +19894,38 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>118068.4177208835</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>116987</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>-1081.417720883546</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0.9908407536769058</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>-0.9159246323094147</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>9082.185978529504</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -19970,7 +19936,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>foremost &gt; --</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -19979,51 +19945,49 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>22334.1243373494</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>22660.8756626506</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>2.014630138185215</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>101.4630138185215</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>4466.82486746988</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -20032,45 +19996,49 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>118068.4177208835</v>
+        <v>56765.89935742972</v>
       </c>
       <c r="D6" t="n">
-        <v>1015</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>1.280788177339901</v>
+        <v>8</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>116987</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>-1081.417720883546</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>0.9908407536769058</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>-0.9159246323094147</v>
+        <v>71992</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>15226.10064257028</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>1.268226185349381</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>26.82261853493815</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>9082.185978529504</v>
+        <v>7095.737419678715</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -20079,45 +20047,49 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>22334.1243373494</v>
+        <v>34548.09858433735</v>
       </c>
       <c r="D7" t="n">
-        <v>192</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>2.604166666666667</v>
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>22660.8756626506</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>2.014630138185215</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>101.4630138185215</v>
+        <v>17998</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>-16550.09858433735</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0.5209548640155709</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>-47.90451359844292</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>4466.82486746988</v>
+        <v>17274.04929216867</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -20126,45 +20098,51 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>56765.89935742972</v>
+        <v>842.8770903010034</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1.639344262295082</v>
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>71992</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>15226.10064257028</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>1.268226185349381</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>26.82261853493815</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>7095.737419678715</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>-842.8770903010034</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>-100</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -20173,34 +20151,38 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>34548.09858433735</v>
+        <v>49561.172909699</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0.6734006734006733</v>
+        <v>5</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>17998</v>
+        <v>44995</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>-16550.09858433735</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>0.5209548640155709</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>-47.90451359844292</v>
+        <v>-4566.172909699002</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0.9078679409379875</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>-9.213205906201249</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>17274.04929216867</v>
+        <v>9912.2345819398</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -20211,7 +20193,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -20220,31 +20202,39 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>842.8770903010034</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>84.28770903010033</v>
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>-842.8770903010034</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>-100</v>
+        <v>26997</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>26997</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -20253,14 +20243,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -20269,45 +20259,55 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>49561.172909699</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>588</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>0.8503401360544218</v>
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>-4566.172909699002</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>0.9078679409379875</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>-9.213205906201249</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>9912.2345819398</v>
+        <v>53994</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>53994</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -20319,22 +20319,26 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>288</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>1.041666666666667</v>
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>26997</v>
+        <v>8999</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -20360,7 +20364,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language</t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -20372,22 +20376,26 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>444</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1.351351351351351</v>
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>53994</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>53994</v>
+        <v>8999</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -20413,7 +20421,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -20425,22 +20433,26 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>35996</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>35996</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -20459,537 +20471,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>30</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
           <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>11</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>9.090909090909092</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; core it professionals | 25 - 55</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>7</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 |</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 |</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>29</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 |</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 |</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>27</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>243</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>1.646090534979424</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>35996</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>35996</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{adset.name}}</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>51</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
@@ -21004,16 +20486,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -21104,21 +20586,25 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>3.448275862068965</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H2" s="2" t="n">
         <v>8999</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="4" t="n">
         <v>8999</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -21145,7 +20631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>chatgpt.com &gt; -- &gt; --</t>
+          <t>fml-p1-002 &gt; coding languages – copy &gt; abhishekpal-ad 2 hook 6-1;1 ratio-311025-006</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -21157,16 +20643,20 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H3" s="2" t="n">
         <v>0</v>
@@ -21198,7 +20688,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fml-p1-002 &gt; coding languages – copy &gt; abhishekpal-ad 2 hook 6-1;1 ratio-311025-006</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience &gt; split screen &lt;&gt; germany is actively hiring international talent right now &gt;</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -21207,40 +20697,38 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>118068.4177208835</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>116987</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>-1081.417720883546</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0.9908407536769058</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>-0.9159246323094147</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>9082.185978529504</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -21251,7 +20739,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>foremost &gt; -- &gt; --</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy &gt; image ad &lt;&gt; sticky note &lt;&gt; join this masterclass, dubai's tech sector is growing fast and sponsoring visas now</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -21260,51 +20748,49 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>22334.1243373494</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>22660.8756626506</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>2.014630138185215</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>101.4630138185215</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>4466.82486746988</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience &gt; split screen &lt;&gt; germany is actively hiring international talent right now &gt;</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -21313,45 +20799,49 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>118068.4177208835</v>
+        <v>28150.3025502008</v>
       </c>
       <c r="D6" t="n">
-        <v>1015</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>1.280788177339901</v>
+        <v>5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>116987</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>-1081.417720883546</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>0.9908407536769058</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>-0.9159246323094147</v>
+        <v>44995</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>16844.6974497992</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>1.598384241865956</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>59.83842418659561</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>9082.185978529504</v>
+        <v>5630.060510040161</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy &gt; image ad &lt;&gt; sticky note &lt;&gt; join this masterclass, dubai's tech sector is growing fast and sponsoring visas now</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; if you want a it job abroad in 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -21360,45 +20850,51 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>22334.1243373494</v>
+        <v>1163.235642570281</v>
       </c>
       <c r="D7" t="n">
-        <v>192</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>2.604166666666667</v>
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>22660.8756626506</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>2.014630138185215</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>101.4630138185215</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>4466.82486746988</v>
+        <v>0</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>-1163.235642570281</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>-100</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; what if i get rejected my english not that good &lt;&gt; navy blue blazer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -21407,45 +20903,49 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>28150.3025502008</v>
+        <v>27452.36116465864</v>
       </c>
       <c r="D8" t="n">
-        <v>242</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>2.066115702479339</v>
+        <v>3</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>16844.6974497992</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>1.598384241865956</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>59.83842418659561</v>
+        <v>26997</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>-455.361164658636</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.9834126776226136</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>-1.658732237738642</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>5630.060510040161</v>
+        <v>9150.787054886212</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; if you want a it job abroad in 2026</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; laptop screen | if you're an it professional in india &amp; looking to get</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -21454,30 +20954,34 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1163.235642570281</v>
+        <v>116.3235642570281</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>-1163.235642570281</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4" t="n">
+        <v>-116.3235642570281</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="n">
         <v>-100</v>
       </c>
       <c r="L9" t="inlineStr">
@@ -21494,7 +20998,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; what if i get rejected my english not that good &lt;&gt; navy blue blazer</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -21503,34 +21007,38 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>27452.36116465864</v>
+        <v>34431.77502008032</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1.271186440677966</v>
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>26997</v>
+        <v>17998</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>-455.361164658636</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>0.9834126776226136</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>-1.658732237738642</v>
+        <v>-16433.77502008032</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0.5227148466642721</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>-47.72851533357279</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>9150.787054886212</v>
+        <v>17215.88751004016</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -21541,7 +21049,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; laptop screen | if you're an it professional in india &amp; looking to get</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -21550,30 +21058,34 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>842.8770903010034</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>-116.3235642570281</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4" t="n">
+        <v>-842.8770903010034</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="n">
         <v>-100</v>
       </c>
       <c r="L11" t="inlineStr">
@@ -21590,7 +21102,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -21599,34 +21111,38 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>34431.77502008032</v>
+        <v>49561.172909699</v>
       </c>
       <c r="D12" t="n">
-        <v>296</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>0.6756756756756757</v>
+        <v>5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>17998</v>
+        <v>44995</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>-16433.77502008032</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>0.5227148466642721</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>-47.72851533357279</v>
+        <v>-4566.172909699002</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0.9078679409379875</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>-9.213205906201249</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>17215.88751004016</v>
+        <v>9912.2345819398</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -21637,7 +21153,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -21646,31 +21162,39 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>842.8770903010034</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>84.28770903010033</v>
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>-842.8770903010034</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>-100</v>
+        <v>26997</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>26997</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -21679,14 +21203,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -21695,45 +21219,55 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>49561.172909699</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>588</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>0.8503401360544218</v>
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>-4566.172909699002</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>0.9078679409379875</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>-9.213205906201249</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>9912.2345819398</v>
+        <v>53994</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>53994</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; --</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -21745,22 +21279,26 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -21779,14 +21317,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt; – copy 2</t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -21798,22 +21336,26 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -21832,14 +21374,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -21851,21 +21393,25 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>286</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F17" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>1.048951048951049</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H17" s="2" t="n">
         <v>26997</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="I17" s="4" t="n">
         <v>26997</v>
       </c>
       <c r="J17" t="inlineStr">
@@ -21892,7 +21438,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremost leads-13-09&lt;do you know which countries are hiring&gt; – copy 2</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -21904,22 +21450,26 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -21938,1120 +21488,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>443</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>6</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>1.354401805869075</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>53994</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>53994</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
           <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55 &gt; split ad 10</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55 &gt; split ad 4</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>7</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>22</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 3</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 5</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>15</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 6</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>7</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 1</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; core it professionals | 25 - 55 &gt; abhishek pal 5</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>7</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | dubai's tech sector is growing fast and sponsoring visas now</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | stop applying to places that were never going to sponsor you. find out who actually does</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 | &gt; image ads | whiteboard | pick the right country for your experience. not just what's trending</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>29</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | sticky notes | germany is short on tech workers and hiring from india right now</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>7</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | whiteboard | know what dutch companies look for before you apply</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 | &gt; image ads | ignored vs shortlisted</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>27</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>72</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>4.166666666666666</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>26997</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>171</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>0.5847953216374269</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{adset.name}} &gt; {{ad.name}}</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>51</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
@@ -23066,16 +21503,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -23166,21 +21603,25 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>3.448275862068965</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H2" s="2" t="n">
         <v>8999</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="4" t="n">
         <v>8999</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -23207,7 +21648,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>chatgpt.com &gt; --</t>
+          <t>fml-p1-002 &gt; instagram_reels</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -23219,16 +21660,20 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H3" s="2" t="n">
         <v>0</v>
@@ -23260,7 +21705,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fml-p1-002 &gt; instagram_reels</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_desktop_feed</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -23269,35 +21714,35 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>465.2942570281124</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I4" s="7" t="n">
+        <v>-465.2942570281124</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>-100</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -23313,7 +21758,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>foremost &gt; --</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_instream_video</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -23322,35 +21767,35 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>465.2942570281124</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I5" s="7" t="n">
+        <v>-465.2942570281124</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>-100</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -23366,7 +21811,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_desktop_feed</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_mobile_feed</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -23375,30 +21820,34 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>465.2942570281124</v>
+        <v>3955.001184738956</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-465.2942570281124</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4" t="n">
+        <v>-3955.001184738956</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6" t="n">
         <v>-100</v>
       </c>
       <c r="L6" t="inlineStr">
@@ -23415,7 +21864,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_instream_video</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_mobile_reels</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -23424,47 +21873,49 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>465.2942570281124</v>
+        <v>12446.62137550201</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>-465.2942570281124</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>17998</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>5551.378624497991</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1.446014902921725</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>44.60149029217246</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>6223.310687751004</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_mobile_feed</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_stories</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -23473,30 +21924,34 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3955.001184738956</v>
+        <v>697.9413855421687</v>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>-3955.001184738956</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4" t="n">
+        <v>-697.9413855421687</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="n">
         <v>-100</v>
       </c>
       <c r="L8" t="inlineStr">
@@ -23513,7 +21968,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_mobile_reels</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; instagram_feed</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -23522,34 +21977,38 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>12446.62137550201</v>
+        <v>25940.15482931727</v>
       </c>
       <c r="D9" t="n">
-        <v>107</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>1.869158878504673</v>
+        <v>3</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>5551.378624497991</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>1.446014902921725</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>44.60149029217246</v>
+        <v>26997</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>1056.845170682729</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>1.040741667797923</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>4.074166779792288</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>6223.310687751004</v>
+        <v>8646.718276439091</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -23560,7 +22019,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; facebook_stories</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; instagram_reels</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -23569,47 +22028,49 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>697.9413855421687</v>
+        <v>170297.6980722892</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>-697.9413855421687</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>197978</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>27680.30192771083</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1.1625406699036</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>16.25406699035996</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>7740.804457831327</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; instagram_feed</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -23618,45 +22079,49 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>25940.15482931727</v>
+        <v>14540.44553212851</v>
       </c>
       <c r="D11" t="n">
-        <v>223</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1.345291479820628</v>
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>1056.845170682729</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>1.040741667797923</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>4.074166779792288</v>
+        <v>8999</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>-5541.445532128515</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0.6188943784504981</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>-38.11056215495018</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>8646.718276439091</v>
+        <v>14540.44553212851</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; instagram_reels</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; others</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -23665,45 +22130,51 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>170297.6980722892</v>
+        <v>2675.441977911647</v>
       </c>
       <c r="D12" t="n">
-        <v>1464</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>1.502732240437158</v>
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>197978</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>27680.30192771083</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>1.1625406699036</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>16.25406699035996</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>7740.804457831327</v>
+        <v>0</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>-2675.441977911647</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>-100</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; instagram_stories</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; threads_feed</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -23712,34 +22183,40 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>14540.44553212851</v>
+        <v>232.6471285140562</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>0.8</v>
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>8999</v>
+        <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>-5541.445532128515</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>0.6188943784504981</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>-38.11056215495018</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>14540.44553212851</v>
+        <v>-232.6471285140562</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>-100</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -23750,7 +22227,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; others</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_instream_video</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -23759,30 +22236,34 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2675.441977911647</v>
+        <v>84.28770903010034</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-2675.441977911647</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4" t="n">
+        <v>-84.28770903010034</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6" t="n">
         <v>-100</v>
       </c>
       <c r="L14" t="inlineStr">
@@ -23799,7 +22280,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; threads_feed</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_mobile_feed</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -23808,30 +22289,34 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>232.6471285140562</v>
+        <v>674.3016722408028</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-232.6471285140562</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="4" t="n">
+        <v>-674.3016722408028</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6" t="n">
         <v>-100</v>
       </c>
       <c r="L15" t="inlineStr">
@@ -23848,7 +22333,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_instream_video</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_mobile_reels</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -23857,47 +22342,49 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>2444.34356187291</v>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>84.28770903010034</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>-84.28770903010034</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>8999</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>6554.65643812709</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>3.681561029458873</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>268.1561029458874</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>2444.34356187291</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_mobile_feed</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_stories</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -23906,30 +22393,34 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>674.3016722408028</v>
+        <v>84.28770903010034</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-674.3016722408028</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4" t="n">
+        <v>-84.28770903010034</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6" t="n">
         <v>-100</v>
       </c>
       <c r="L17" t="inlineStr">
@@ -23946,7 +22437,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_mobile_reels</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; instagram_feed</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -23955,45 +22446,51 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2444.34356187291</v>
+        <v>2612.918979933111</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>3.448275862068965</v>
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>6554.65643812709</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>3.681561029458873</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>268.1561029458874</v>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>2444.34356187291</v>
+        <v>0</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>-2612.918979933111</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>-100</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; facebook_stories</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; instagram_reels</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -24002,36 +22499,38 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>43576.74556856188</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0</v>
+        <v>35996</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-84.28770903010034</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>-7580.745568561877</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0.8260369040952211</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>-17.39630959047788</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>10894.18639214047</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -24042,7 +22541,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; instagram_feed</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -24051,30 +22550,34 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2612.918979933111</v>
+        <v>758.5893812709031</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="4" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>-2612.918979933111</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="4" t="n">
+        <v>-758.5893812709031</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="n">
         <v>-100</v>
       </c>
       <c r="L20" t="inlineStr">
@@ -24091,7 +22594,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; instagram_reels</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; others</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -24100,34 +22603,40 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>43576.74556856188</v>
+        <v>168.5754180602007</v>
       </c>
       <c r="D21" t="n">
-        <v>517</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0.7736943907156674</v>
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>35996</v>
+        <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>-7580.745568561877</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>0.8260369040952211</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>-17.39630959047788</v>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>10894.18639214047</v>
+        <v>-168.5754180602007</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>-100</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -24138,7 +22647,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; instagram_stories</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; facebook_mobile_feed</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -24147,31 +22656,39 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>758.5893812709031</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>-758.5893812709031</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>-100</v>
+        <v>8999</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>8999</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -24180,14 +22697,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; others</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; facebook_mobile_reels</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -24196,31 +22713,39 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>168.5754180602007</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>-168.5754180602007</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>-100</v>
+        <v>26997</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>26997</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -24229,14 +22754,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; facebook_instream_video</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; instagram_feed</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -24248,22 +22773,26 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -24282,14 +22811,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; facebook_mobile_feed</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; instagram_reels</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -24301,22 +22830,26 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>3.333333333333333</v>
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>8999</v>
+        <v>17998</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>17998</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -24342,7 +22875,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; facebook_mobile_reels</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -24354,22 +22887,26 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>162</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>1.851851851851852</v>
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>26997</v>
+        <v>8999</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -24395,7 +22932,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; facebook_stories</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; others</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -24407,22 +22944,26 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -24441,14 +22982,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; instagram_feed</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; instagram_feed</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -24460,21 +23001,25 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>99</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="n">
-        <v>1.01010101010101</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H28" s="2" t="n">
         <v>8999</v>
       </c>
-      <c r="I28" s="5" t="n">
+      <c r="I28" s="4" t="n">
         <v>8999</v>
       </c>
       <c r="J28" t="inlineStr">
@@ -24501,7 +23046,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; instagram_reels</t>
+          <t>foremost leads | cbo | 14th august &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -24513,22 +23058,26 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>378</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>0.5291005291005291</v>
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>17998</v>
+        <v>8999</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -24554,7 +23103,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; instagram_search</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_desktop_feed</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -24566,16 +23115,20 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="4" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H30" s="2" t="n">
         <v>0</v>
@@ -24607,7 +23160,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; instagram_stories</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_instream_video</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -24619,22 +23172,26 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>2.272727272727273</v>
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -24653,14 +23210,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; others</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_mobile_feed</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -24672,22 +23229,26 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -24706,14 +23267,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; facebook_instream_video</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_mobile_reels</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -24725,16 +23286,20 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="4" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H33" s="2" t="n">
         <v>0</v>
@@ -24766,7 +23331,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; facebook_mobile_feed</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_notification</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -24778,16 +23343,20 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="4" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H34" s="2" t="n">
         <v>0</v>
@@ -24819,7 +23388,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; facebook_mobile_reels</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_stories</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -24831,16 +23400,20 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>22</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="4" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H35" s="2" t="n">
         <v>0</v>
@@ -24872,7 +23445,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; instagram_feed</t>
+          <t>foremostleads-gs-13-09 &gt; instagram_feed</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -24884,21 +23457,25 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="4" t="n">
-        <v>12.5</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H36" s="2" t="n">
         <v>8999</v>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="I36" s="4" t="n">
         <v>8999</v>
       </c>
       <c r="J36" t="inlineStr">
@@ -24925,7 +23502,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; instagram_reels</t>
+          <t>foremostleads-gs-13-09 &gt; instagram_reels</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -24937,22 +23514,26 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>21</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>17998</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>17998</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -24971,14 +23552,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; instagram_stories</t>
+          <t>foremostleads-gs-13-09 &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -24990,22 +23571,26 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>8999</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -25024,1173 +23609,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; facebook_instream_video</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; facebook_mobile_reels</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; instagram_feed</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; instagram_reels</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
-        <v>5</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 14th august &gt; instagram_stories</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
           <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; facebook_mobile_feed</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>16</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; facebook_mobile_reels</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>16</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_feed</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>13</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_reels</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
-        <v>6</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_stories</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>13</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; others</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; threads_feed</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_desktop_feed</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_instream_video</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_mobile_feed</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="n">
-        <v>7</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_mobile_reels</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>23</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_notification</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_stories</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
-        <v>4</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; instagram_feed</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>24</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="4" t="n">
-        <v>4.166666666666666</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I57" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; instagram_reels</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>149</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>1.342281879194631</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>17998</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; instagram_stories</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="n">
-        <v>30</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="4" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I59" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{placement}}</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="n">
-        <v>51</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
@@ -26291,7 +23710,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26301,7 +23720,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26311,7 +23730,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
